--- a/output/pdf_financials_xlsx/OMM.xlsx
+++ b/output/pdf_financials_xlsx/OMM.xlsx
@@ -6480,25 +6480,25 @@
         <v>0.142972</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>13.821226</v>
+        <v>13.823865</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.476276</v>
+        <v>0.138133</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.548878</v>
+        <v>0.16726</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.574999</v>
+        <v>0.500437</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.643482</v>
+        <v>0.638907</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.826132</v>
+        <v>0.754615</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.108632</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>0</v>
@@ -17836,7 +17836,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OMM.xlsx
+++ b/output/pdf_financials_xlsx/OMM.xlsx
@@ -972,13 +972,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.011084</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.00132</v>
       </c>
     </row>
     <row r="13">
@@ -1835,13 +1835,13 @@
         <v>-2.075853</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.100688</v>
+        <v>-2.111772</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-2.647216</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-2.647216</v>
+        <v>-2.648536</v>
       </c>
     </row>
     <row r="28">
@@ -1933,13 +1933,13 @@
         <v>-2.072959</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.100688</v>
+        <v>-2.111772</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-2.647216</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.647216</v>
+        <v>-2.648536</v>
       </c>
     </row>
     <row r="30">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -24458,7 +24458,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -25706,7 +25706,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">

--- a/output/pdf_financials_xlsx/OMM.xlsx
+++ b/output/pdf_financials_xlsx/OMM.xlsx
@@ -6183,19 +6183,19 @@
         <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.021464</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.166099</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>4.8e-05</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -18726,7 +18726,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -19614,7 +19618,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/OMM.xlsx
+++ b/output/pdf_financials_xlsx/OMM.xlsx
@@ -6109,16 +6109,16 @@
         <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.126159</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.141986</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.159801</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.179849</v>
       </c>
     </row>
     <row r="111">
@@ -6327,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.501569</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -6342,13 +6342,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.024882</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.00362</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.004448</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -6360,7 +6360,7 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.005781</v>
       </c>
       <c r="O115" s="3" t="n">
         <v>0</v>
@@ -14056,7 +14056,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -15078,7 +15082,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -17588,7 +17596,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -17986,7 +17998,11 @@
           <t>Proceeds from shares issued</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -22884,7 +22900,11 @@
           <t>Proceeds from the sale of investments</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
